--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1898,6 +1898,335 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>US-31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Tenant admin</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>to register my tenant with its name, my email and a password</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>my team gets its own private workspace</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Password &gt;= 10 characters, stored hashed with BCrypt; email unique (case-insensitive)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>US-32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>to log in and log out</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>only my team can see our data</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Server session in an HttpOnly, SameSite=Lax cookie; CSRF token on every state-changing request; generic "invalid email or password" message; every `/api` endpoint except register and login returns 401 without a session</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>US-33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Tenant admin</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>the imports, maps and plans of my tenant to be invisible to any other tenant</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>our confidential revenue data stays private (NDA)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Enforced by one backend guard on all `/api/imports/{id}/**` and `/api/plans/{planId}/**` routes; another tenant's id returns 404, not 403; covered by an automated isolation test</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>US-34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Tenant admin</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>to register the enterprises of my tenant (name, column header in our ERP export, color and optionally VAT number and headquarters address), at registration or later</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>I enter them once instead of at every import</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>S12, S13</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Optional at registration; name and ERP column unique per tenant (case-insensitive); headquarters geocoded with the same cache and rate limit as delivery points</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>US-35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>the import wizard to match the file columns to my registered enterprises and pre-fill their names, colors and addresses</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>importing a new yearly file takes fewer steps</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Case- and accent-insensitive match on the ERP column, then on the name; numeric columns that match nothing are still suggested as new enterprises</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>US-36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>to change the enterprise data (including the headquarters address) for a single import in the wizard</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>I can try alternatives and see how they change the results</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Values copied into the import (snapshot); the profile changes only if "Also save to profile" is ticked; editing the profile never changes existing imports</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>US-37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Tenant admin</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>a profile page to change the tenant name, my password and the enterprises</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>our information stays up to date</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Password change requires the current password; deleting an enterprise does not change existing imports</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1909,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2116,6 +2445,40 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Register / Log in</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mockups/S12-*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tenant profile</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mockups/S13-*.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Password &gt;= 10 characters, stored hashed with BCrypt; email unique (case-insensitive)</t>
+          <t>One account per tenant; password 8-64 characters (minimum configurable), no composition rules, stored hashed with Argon2id (OWASP ASVS 5.0); email unique (case-insensitive)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>a profile page to change the tenant name, my password and the enterprises</t>
+          <t>a profile page to change the tenant name, the password and the enterprises</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Password change requires the current password; deleting an enterprise does not change existing imports</t>
+          <t>Password change requires the current password and logs out the other sessions; deleting an enterprise does not change existing imports</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>to set the visit parameters (visit duration, working hours, starting point, maximum distance)</t>
+          <t>to set the visit parameters (visit duration, working hours, maximum distance)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Defaults: visit 210 min, workday 480 min, base Rome centre, max 80 km; invalid values rejected with a clear message</t>
+          <t>Defaults: visit 210 min, workday 480 min, max 80 km; every day starts and ends at the tenant starting base (US-35); invalid values rejected with a clear message</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>to register the enterprises of my tenant (name, column header in our ERP export, color and optionally VAT number and headquarters address), at registration or later</t>
+          <t>a profile page to change the tenant name and the password</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>I enter them once instead of at every import</t>
+          <t>our information stays up to date</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>S12, S13</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Optional at registration; name and ERP column unique per tenant (case-insensitive); headquarters geocoded with the same cache and rate limit as delivery points</t>
+          <t>Password change requires the current password and logs out the other sessions</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>the import wizard to match the file columns to my registered enterprises and pre-fill their names, colors and addresses</t>
+          <t>to set the starting base of my tenant once by typing its address in the planner</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>importing a new yearly file takes fewer steps</t>
+          <t>every plan starts from our real base without entering it again</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2124,104 +2124,10 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Case- and accent-insensitive match on the ERP column, then on the name; numeric columns that match nothing are still suggested as new enterprises</t>
+          <t>One base per tenant, stored in the database; address + city geocoded with the Nominatim cache and rate limit; address not found -&gt; clear message and the saved base unchanged; until a base is set the planner uses the configured default (Rome centre)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>US-36</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>to change the enterprise data (including the headquarters address) for a single import in the wizard</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>I can try alternatives and see how they change the results</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Puccetti</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Values copied into the import (snapshot); the profile changes only if "Also save to profile" is ticked; editing the profile never changes existing imports</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>US-37</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Tenant admin</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>a profile page to change the tenant name, the password and the enterprises</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>our information stays up to date</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>S13</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Puccetti</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Password change requires the current password and logs out the other sessions; deleting an enterprise does not change existing imports</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2128,6 +2128,53 @@
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>US-36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>to switch the interface between light and dark mode</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>I can work comfortably in any light</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>All (header)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Follows the operating system setting until the user chooses; the choice is remembered in the browser; no flash of the wrong theme on load; toggle reachable by keyboard with its state announced to screen readers; text contrast WCAG AA in both themes; also available before login</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2175,53 @@
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>US-37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>to stay logged in on my own device</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>I do not have to type my credentials every day</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Opt-in checkbox at login, off by default; 14 days (configurable); HttpOnly, SameSite=Lax, Secure over HTTPS cookie; random token stored server-side and replaced at every use, reuse of an old token logs out every remembered device; logout forgets this device only, password change forgets every device; the password is never stored by the application</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -1518,7 +1518,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DOING</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DOING</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DOING</t>
         </is>
       </c>
     </row>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="User stories" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Screens" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User stories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screens" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User stories" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screens" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="User stories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Screens" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2224,6 +2224,53 @@
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>US-38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>a modern and consistent interface where the key figures stand out</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>I can read the data at a glance</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Same design tokens in light and dark mode; text contrast WCAG AA in both; one brand color for highlights only, never for data (enterprise colors stay the only data colors); pill navigation usable by keyboard with the current page announced; layout usable from 375 px wide; no new dependency (system font)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>TODO</t>
         </is>
       </c>
     </row>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2271,6 +2271,53 @@
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>US-39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>the planner to use real road distances and driving times</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>every planned day can really be driven within the working hours</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Puccetti</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Optional self-hosted OSRM (Docker Compose profile with the OpenStreetMap extract of central Italy), so customer coordinates never leave the system; one distance and time table per import and base, about 1 s for 1,000 points and kept in memory; when the road network is off or unreachable the plan uses the straight-line estimate and says which one it used</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>

--- a/booklets/user-stories/user-stories.xlsx
+++ b/booklets/user-stories/user-stories.xlsx
@@ -2270,7 +2270,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
